--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261019.xlsx
@@ -13357,7 +13357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15221,30 +15221,30 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>T42</t>
+          <t>T43</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>町データ待ちの切り分け（公表資料・見える化で拾えるものを分ける）</t>
+          <t>法令APIで条文を確定し、条文番号の原典確認の検査を新設</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>手元の資料と見える化の出力を当たるだけで分かる。町にお尋ねする数が多いほど回答が遅れ、計画が止まる。当方で取れるものを取り切ってから残りをお尋ねする</t>
+          <t>10月19日に環境が更新され、e-Gov 法令API への接続が許可された。引いている条・項・号をその場で確かめられる。かねて「条文番号は突合の対象外」としていた穴がふさがる</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>16_町データ依頼／町データ待ちの切り分け（50件を4区分）</t>
+          <t>check_ono_jobun.py（22件）／内部検討 法令APIによる条文の確定</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>1-6／障がい 1-6</t>
+          <t>11-1／8-9</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -15266,57 +15266,102 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>T42</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>町データ待ちの切り分け（公表資料・見える化で拾えるものを分ける）</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>手元の資料と見える化の出力を当たるだけで分かる。町にお尋ねする数が多いほど回答が遅れ、計画が止まる。当方で取れるものを取り切ってから残りをお尋ねする</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>16_町データ依頼／町データ待ちの切り分け（50件を4区分）</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>1-6／障がい 1-6</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>10月19日（月）</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>10月19日（月）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>T32</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>障がい計画　成果目標とサービス見込量の算定</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>算定の方式は素案 第3部第2章に置いた。ただし値そのものはサービス別実績（町データ）が要るため、いま進められるのは方式の精査までである</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D44" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>障がい計画 素案 第2版</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>障がい 6-3／障がい 6-4</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>10月20日（火）</t>
         </is>
       </c>
-      <c r="H43" s="12" t="inlineStr">
+      <c r="H44" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>※ 合計 117.0時間（1日 8.0時間として約14.6日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>※ 合計 120.0時間（1日 8.0時間として約15.0日）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>※ 「なぜ今できるか」に町の回答待ちが混ざっている項目があると、ブックの生成が止まります。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261019.xlsx
@@ -926,7 +926,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>保険料基準額（基金取崩額を通じて月額240円の幅）</t>
+          <t>保険料基準額（基金取崩額を通じて月額1,719円の幅）</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>年報 様式4 の12,000千円で据え置き、取崩なしを標準ケースにする</t>
+          <t>町の財務書類の残高（令和8年度末見込210,000千円）を前提に、取崩なしを標準ケースにする</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>保険料基準額（取崩なし6,048円／12,000千円全額6,000円弱／第9期と同じ35,000千円5,808円。幅240円）</t>
+          <t>保険料基準額（取崩なし6,053円／105,000千円（令和8年度末見込の半分）5,194円／210,000千円（全額）4,334円。幅1,719円）</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>年報 様式4 の12,000千円を保守的な前提として置き、取崩なしのケースを標準にする。基金運用状況調書（依頼1）が出たら差し替える</t>
+          <t>町の財務書類の残高（令和8年度末見込210,000千円）を前提に、取崩なしのケースを標準にする。令和7年度末の残高（財産に関する調書）が出たら差し替える</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>保険料基準額（取崩なし6,048円／12,000千円全額6,000円弱／第9期と同じ35,000千円5,808円。幅240円）</t>
+          <t>保険料基準額（取崩なし6,053円／105,000千円（令和8年度末見込の半分）5,194円／210,000千円（全額）4,334円。幅1,719円）</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>保険料基準額（基金取崩額を通じて月額240円の幅）</t>
+          <t>保険料基準額（基金取崩額を通じて月額1,719円の幅）</t>
         </is>
       </c>
     </row>
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="I124" s="13" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J124" s="13" t="n">
         <v>26.7</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>65.3</v>
+        <v>68.3</v>
       </c>
       <c r="L124" s="5" t="n">
         <v>4</v>
@@ -13314,7 +13314,7 @@
     <row r="129">
       <c r="A129" s="19" t="inlineStr">
         <is>
-          <t>高齢者計画　予定進捗率 62.2％　対　実績進捗率 71.2％　乖離 +9.0ポイント　／　おおむね予定どおり 51件／前倒し 17件／遅れ 5件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>高齢者計画　予定進捗率 62.2％　対　実績進捗率 71.2％　乖離 +9.1ポイント　／　おおむね予定どおり 51件／前倒し 17件／遅れ 5件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19892,7 @@
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="117">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261019.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261019.xlsx
@@ -9083,7 +9083,7 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の様式4が全て0で未入力。また基金保有額が令和4年度末120百万円から令和5年度末12百万円へ1桁減っており、取崩実績か入力誤りかの確認が要る</t>
+          <t>令和7年度の様式4が全て0で未入力。年報 様式4の基金保有額（令和5・6年度末12百万円）は財務書類と合わない。基金は令和8年度末見込210.0百万円。令和7年度末の残高（財産に関する調書）の確認が要る</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>―　9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。認知症の設問の項目名を1件訂正し、報告書そのものの食い違い3件を注記した</t>
+          <t>―　9月29日に調査結果報告書の原本（104頁）を受領し、集計値を1件ずつ突き合わせた（286件・NG0）。認知症の設問の項目名を原本に合わせ、報告書そのものの食い違い3件を注記した</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="N118" s="6" t="inlineStr">
         <is>
-          <t>9月24日に、受託者が算定すべき未確定箇所をすべて解消した。所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。あわせて数値の誤りを2件正した。①所得第2段階の乗率を年報 様式1 所得段階別の令和7年度の値により0.486としたが、これは誤りで0.485が正しい（9月25日に再訂正）。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和6年度は485であり、令和7年度の486が入力誤りである。②所得第1〜3段階の割合を28％としていたが、1,094人÷3,443人で31.8％が正しい。第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
+          <t>9月24日に、受託者が算定すべき未確定箇所をすべて解消した。所得段階別保険料率を13段階すべてについて算定し（乗率・年額・被保険者数・構成比）、必要利用定員総数・地域支援事業の量・認知症高齢者数を加えた。未確定は158箇所→94箇所となり、【算定後に記載】は0件になった。あわせて数値2件を原本で確かめた。①所得第2段階の乗率は0.485とした。第9期計画本文が「基準額×0.485」「年額38,500円」と明記しており、79,200円×0.485＝38,412円の100円未満切上げで38,500円になる。年報の令和7年度は486となっているが、令和6年度は485である。②所得第1〜3段階の割合は、1,094人÷3,443人で31.8％である。第2章1の人口（見える化の将来推計・暦年）と第2章6の被保険者数（第10期将来推計用推計人口・年度）が別系列であることを注記した。従前の注は「保険料算定との整合のため見える化の推計を用いる」と書いていたが、保険料算定は後者を用いており誤りであった</t>
         </is>
       </c>
     </row>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
-          <t>一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、第9期が見込んだ基金取崩35,000千円に対し基金保有額が12,000千円しかない点の確認が要る（しかも年報の残高の系列に矛盾がある）</t>
+          <t>一般介護予防事業費と包括的支援事業・任意事業費の事業別内訳、令和7年度の決算額（年報が未入力）、調整交付金見込額、第10期の第1号被保険者負担割合。あわせて、令和7年度末の基金残高（財産に関する調書）の確認が要る。第9期が見込んだ基金取崩35,000千円は残高の範囲内で実行できる</t>
         </is>
       </c>
     </row>
